--- a/exame_basico.xlsx
+++ b/exame_basico.xlsx
@@ -5,22 +5,35 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://c24hs-my.sharepoint.com/personal/posilva_central24horas_com_br/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://c24hs-my.sharepoint.com/personal/posilva_central24horas_com_br/Documents/Projetos/RH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94D0E5DC-C749-42EE-A24C-91FAF227DEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{922B79BB-E317-4800-BAE8-83FE8F3AFD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4E4B453-B84B-4A9C-87FE-9B435F3A7101}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Teste de Excel" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Teste de conhecimentos de Excel</t>
   </si>
@@ -31,52 +44,72 @@
     <t>Quantidade</t>
   </si>
   <si>
-    <t>Valor (R$)</t>
-  </si>
-  <si>
-    <t>Sub Total</t>
-  </si>
-  <si>
     <t>Processador</t>
   </si>
   <si>
-    <t>Indira</t>
-  </si>
-  <si>
     <t>Placa mãe</t>
   </si>
   <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>1) Insira linhas de grade na planilha acima.</t>
-  </si>
-  <si>
-    <t>2) Copie a planilha acima para a célula G9.</t>
-  </si>
-  <si>
-    <t>3) Coloque o preenchimento Azul claro na célula D9.</t>
-  </si>
-  <si>
-    <t>4) Insira um comentário na célula A11.</t>
-  </si>
-  <si>
-    <t>5) Insira filtro na planilha.</t>
-  </si>
-  <si>
-    <t>6) Calcule o total dos produtos inserindo fórmula.</t>
-  </si>
-  <si>
     <t>Questões</t>
+  </si>
+  <si>
+    <t>1) Insira uma coluna de Subtotal ao final da planilha e depois calcule o valor do produto pela sua quantidade.</t>
+  </si>
+  <si>
+    <t>Memória RAM</t>
+  </si>
+  <si>
+    <t>Placa de Vídeo</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Valor Unitário (R$)</t>
+  </si>
+  <si>
+    <t>4) Altere a cor do preenchimento para Azul claro na célula A1, e adicione novas cores á linha A2 correspondetes a coluna.</t>
+  </si>
+  <si>
+    <t>3) Adicione o mesmo estilo atual das células da planilha á coluna nova.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2) Converta o valor da coluna 'Valor Unitário' e da coluna 'Subtotal' para o formato contábel. </t>
+  </si>
+  <si>
+    <t>5) Insira filtro na tabela e ordene os produto de maior valor para o de menor valor unitário.</t>
+  </si>
+  <si>
+    <t>6) Insira uma linha de total ao final da Tabela e depois calcule o total das colunas 'Quantidade' e 'Valor R$'.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -200,22 +233,27 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +263,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -568,51 +615,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.875" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="6.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
+      <c r="D1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3">
-        <v>170</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -620,101 +668,125 @@
       <c r="C4" s="3">
         <v>120</v>
       </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
         <v>7</v>
       </c>
-      <c r="B5" s="3">
+      <c r="C6" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3">
-        <v>250</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B7" s="3">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="3">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15.75" x14ac:dyDescent="0.25"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+    </row>
+    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="D8 A7 A15:D15 D17 D18 D19 D20 D21 D22 D16 D14" numberStoredAsText="1"/>
+    <ignoredError sqref="D11 A10 A19:D19 D21 D22 D23 D24 D25 D26 D20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>